--- a/data/Wohlen (AG)/cost/cost_report.xlsx
+++ b/data/Wohlen (AG)/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2697.520626273997</v>
+        <v>2167.584481752182</v>
       </c>
       <c r="C2" t="n">
-        <v>35772.51153625257</v>
+        <v>36053.36818296081</v>
       </c>
       <c r="D2" t="n">
-        <v>107116.318707953</v>
+        <v>120185.7491229404</v>
       </c>
       <c r="E2" t="n">
-        <v>7359.266488826663</v>
+        <v>6805.44564492476</v>
       </c>
       <c r="F2" t="n">
-        <v>68715.07384780482</v>
+        <v>64597.98069526446</v>
       </c>
       <c r="G2" t="n">
-        <v>221660.6912071111</v>
+        <v>229810.1281278426</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.110703415422264</v>
+        <v>0.1147734672477829</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2697.720569425609</v>
+        <v>2180.343404477126</v>
       </c>
       <c r="C3" t="n">
-        <v>35097.01758270913</v>
+        <v>29250.4623975773</v>
       </c>
       <c r="D3" t="n">
-        <v>108561.8112244751</v>
+        <v>147813.1288344616</v>
       </c>
       <c r="E3" t="n">
-        <v>7441.099834518536</v>
+        <v>6927.841624607616</v>
       </c>
       <c r="F3" t="n">
-        <v>70615.8604582151</v>
+        <v>57703.02180016296</v>
       </c>
       <c r="G3" t="n">
-        <v>224413.5096693435</v>
+        <v>243874.7980612866</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1120782482992482</v>
+        <v>0.121797748323241</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2697.434567110678</v>
+        <v>2171.132509131812</v>
       </c>
       <c r="C4" t="n">
-        <v>28979.94998302611</v>
+        <v>29622.26913770285</v>
       </c>
       <c r="D4" t="n">
-        <v>135448.1015758516</v>
+        <v>149141.4464456412</v>
       </c>
       <c r="E4" t="n">
-        <v>7464.250628788926</v>
+        <v>6785.516751405826</v>
       </c>
       <c r="F4" t="n">
-        <v>61028.4170848911</v>
+        <v>53373.80076508544</v>
       </c>
       <c r="G4" t="n">
-        <v>235618.1538396684</v>
+        <v>241094.1656089672</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1176741542376952</v>
+        <v>0.1204090243784161</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2700.927211132745</v>
+        <v>2181.392284381572</v>
       </c>
       <c r="C5" t="n">
-        <v>29298.12044426274</v>
+        <v>35280.86362873802</v>
       </c>
       <c r="D5" t="n">
-        <v>136070.7385659401</v>
+        <v>121484.1989781179</v>
       </c>
       <c r="E5" t="n">
-        <v>7396.48826890348</v>
+        <v>6925.477424134315</v>
       </c>
       <c r="F5" t="n">
-        <v>57432.16905040653</v>
+        <v>66759.26681477661</v>
       </c>
       <c r="G5" t="n">
-        <v>232898.4435406456</v>
+        <v>232631.1991301485</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1163158564834957</v>
+        <v>0.116182387311161</v>
       </c>
     </row>
   </sheetData>
